--- a/resource/deta_godo.xlsx
+++ b/resource/deta_godo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cre\Desktop\ddd\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903E842B-469E-4737-9133-0BC31F499A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572AB9B7-50D2-4E29-AE2F-8D573DAA2D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31785" yWindow="3075" windowWidth="21600" windowHeight="11332" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ステージ" sheetId="1" r:id="rId1"/>
@@ -3126,16 +3126,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>ステージクリア時の回復量+10%</t>
-    <rPh sb="7" eb="8">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="9" eb="12">
-      <t>カイフクリョウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>何をさせたいスキル？：消化時間を減らしたい
 一番気持ちいい使い方：消化時間超減らし
 残基：１
@@ -4184,6 +4174,16 @@
   </si>
   <si>
     <t>カプチーノ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ステージクリア時HP10%回復</t>
+    <rPh sb="7" eb="8">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイフク</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -4718,7 +4718,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I819"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
@@ -17247,7 +17247,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C959AC5-8D67-4CF8-8D3F-6E3C60C27AAC}">
   <dimension ref="A2:Z44"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="1:26">
       <c r="A2" s="8" t="s">
@@ -17269,10 +17269,10 @@
         <v>267</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="X2" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -17296,13 +17296,13 @@
         <v>268</v>
       </c>
       <c r="U3" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" ht="17.649999999999999" customHeight="1">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="17.7" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>249</v>
       </c>
@@ -17324,11 +17324,11 @@
       </c>
       <c r="R4" s="7"/>
       <c r="U4" s="36" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="V4" s="37"/>
       <c r="Y4" s="36" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Z4" s="36"/>
     </row>
@@ -17418,7 +17418,7 @@
       <c r="U9" s="44"/>
       <c r="V9" s="44"/>
       <c r="Y9" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" spans="1:26">
@@ -17429,7 +17429,7 @@
       <c r="U10" s="44"/>
       <c r="V10" s="44"/>
       <c r="Y10" s="36" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Z10" s="37"/>
     </row>
@@ -17440,7 +17440,7 @@
       <c r="Y11" s="37"/>
       <c r="Z11" s="37"/>
     </row>
-    <row r="12" spans="1:26" ht="17.649999999999999" customHeight="1">
+    <row r="12" spans="1:26" ht="17.7" customHeight="1">
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
       <c r="U12" s="44"/>
@@ -17469,7 +17469,7 @@
     </row>
     <row r="16" spans="1:26">
       <c r="Y16" s="36" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Z16" s="37"/>
     </row>
@@ -17487,12 +17487,12 @@
     </row>
     <row r="20" spans="25:26">
       <c r="Y20" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="21" spans="25:26">
       <c r="Y21" s="36" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Z21" s="37"/>
     </row>
@@ -17510,12 +17510,12 @@
     </row>
     <row r="25" spans="25:26">
       <c r="Y25" s="8" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="26" spans="25:26" ht="17.649999999999999" customHeight="1">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="26" spans="25:26" ht="17.7" customHeight="1">
       <c r="Y26" s="36" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Z26" s="36"/>
     </row>
@@ -17537,12 +17537,12 @@
     </row>
     <row r="31" spans="25:26">
       <c r="Y31" s="8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="32" spans="25:26" ht="17.7" customHeight="1">
+      <c r="Y32" s="36" t="s">
         <v>339</v>
-      </c>
-    </row>
-    <row r="32" spans="25:26" ht="17.649999999999999" customHeight="1">
-      <c r="Y32" s="36" t="s">
-        <v>340</v>
       </c>
       <c r="Z32" s="36"/>
     </row>
@@ -17577,7 +17577,7 @@
     </row>
     <row r="40" spans="25:26">
       <c r="Y40" s="36" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Z40" s="37"/>
     </row>
@@ -17624,7 +17624,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:D17"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
@@ -17772,7 +17772,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:D4"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
@@ -17807,7 +17807,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:D3"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
@@ -17834,9 +17834,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="35.375" customWidth="1"/>
+    <col min="1" max="1" width="35.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18304,12 +18304,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA5628B-57DF-418D-BF0F-E86C8FCA0DD9}">
   <dimension ref="B2:F30"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="19.875" customWidth="1"/>
-    <col min="3" max="3" width="90.75" customWidth="1"/>
-    <col min="4" max="4" width="40.125" customWidth="1"/>
-    <col min="5" max="5" width="43.75" customWidth="1"/>
+    <col min="2" max="2" width="19.8984375" customWidth="1"/>
+    <col min="3" max="3" width="90.69921875" customWidth="1"/>
+    <col min="4" max="4" width="40.09765625" customWidth="1"/>
+    <col min="5" max="5" width="43.69921875" customWidth="1"/>
     <col min="6" max="6" width="67.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18815,7 +18815,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FDAC726-4736-4806-81DB-E0C12BC01725}">
   <dimension ref="A1:Z370"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:26">
       <c r="A1" s="41" t="s">
@@ -19124,7 +19124,7 @@
       <c r="D11" s="34"/>
       <c r="E11" s="34"/>
       <c r="F11" s="36" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G11" s="37"/>
       <c r="H11" s="37"/>
@@ -19136,7 +19136,7 @@
       <c r="L11" s="34"/>
       <c r="M11" s="34"/>
       <c r="N11" s="39" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O11" s="40"/>
       <c r="P11" s="40"/>
@@ -19416,7 +19416,7 @@
       <c r="D21" s="34"/>
       <c r="E21" s="34"/>
       <c r="F21" s="36" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G21" s="37"/>
       <c r="H21" s="37"/>
@@ -19439,7 +19439,7 @@
       <c r="U21" s="40"/>
       <c r="V21" s="40"/>
       <c r="W21" s="36" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="X21" s="37"/>
       <c r="Y21" s="37"/>
@@ -19708,7 +19708,7 @@
       <c r="D31" s="34"/>
       <c r="E31" s="34"/>
       <c r="F31" s="36" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G31" s="37"/>
       <c r="H31" s="37"/>
@@ -20000,7 +20000,7 @@
       <c r="D41" s="34"/>
       <c r="E41" s="34"/>
       <c r="F41" s="36" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G41" s="37"/>
       <c r="H41" s="37"/>
@@ -20023,7 +20023,7 @@
       <c r="U41" s="40"/>
       <c r="V41" s="40"/>
       <c r="W41" s="36" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="X41" s="37"/>
       <c r="Y41" s="37"/>
@@ -20294,7 +20294,7 @@
       <c r="D51" s="34"/>
       <c r="E51" s="34"/>
       <c r="F51" s="36" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G51" s="37"/>
       <c r="H51" s="37"/>
@@ -20586,7 +20586,7 @@
       <c r="D61" s="34"/>
       <c r="E61" s="34"/>
       <c r="F61" s="36" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G61" s="37"/>
       <c r="H61" s="37"/>
@@ -20878,7 +20878,7 @@
       <c r="D71" s="34"/>
       <c r="E71" s="34"/>
       <c r="F71" s="36" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G71" s="37"/>
       <c r="H71" s="37"/>
@@ -20890,7 +20890,7 @@
       <c r="L71" s="34"/>
       <c r="M71" s="34"/>
       <c r="N71" s="39" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O71" s="40"/>
       <c r="P71" s="40"/>
@@ -21170,7 +21170,7 @@
       <c r="D81" s="34"/>
       <c r="E81" s="34"/>
       <c r="F81" s="36" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G81" s="37"/>
       <c r="H81" s="37"/>
@@ -21464,7 +21464,7 @@
       <c r="D91" s="34"/>
       <c r="E91" s="34"/>
       <c r="F91" s="36" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G91" s="37"/>
       <c r="H91" s="37"/>
@@ -21476,7 +21476,7 @@
       <c r="L91" s="34"/>
       <c r="M91" s="34"/>
       <c r="N91" s="39" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O91" s="40"/>
       <c r="P91" s="40"/>
@@ -21756,7 +21756,7 @@
       <c r="D101" s="34"/>
       <c r="E101" s="34"/>
       <c r="F101" s="36" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G101" s="37"/>
       <c r="H101" s="37"/>
@@ -22048,7 +22048,7 @@
       <c r="D111" s="34"/>
       <c r="E111" s="34"/>
       <c r="F111" s="36" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G111" s="37"/>
       <c r="H111" s="37"/>
@@ -22340,7 +22340,7 @@
       <c r="D121" s="34"/>
       <c r="E121" s="34"/>
       <c r="F121" s="36" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G121" s="37"/>
       <c r="H121" s="37"/>
@@ -29884,7 +29884,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6D2EFC-47F0-4DB9-83BC-DD958DB4244A}">
   <dimension ref="A1:Z445"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:26">
       <c r="A1" s="38" t="s">
@@ -31072,7 +31072,7 @@
       <c r="H43" s="36"/>
       <c r="I43" s="36"/>
       <c r="J43" s="36" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K43" s="36"/>
       <c r="L43" s="36"/>
@@ -31444,7 +31444,7 @@
       <c r="D56" s="38"/>
       <c r="E56" s="38"/>
       <c r="F56" s="36" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G56" s="36"/>
       <c r="H56" s="36"/>
@@ -31822,7 +31822,7 @@
       <c r="D69" s="38"/>
       <c r="E69" s="38"/>
       <c r="F69" s="36" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G69" s="36"/>
       <c r="H69" s="36"/>
@@ -43025,7 +43025,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCCBED2E-6CBB-4FE7-BB78-40B976DF6037}">
   <dimension ref="A1:Z260"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:26">
       <c r="A1" s="41" t="s">
@@ -43413,7 +43413,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D14" s="38"/>
       <c r="E14" s="38"/>
@@ -43791,18 +43791,18 @@
         <v>2</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D27" s="38"/>
       <c r="E27" s="38"/>
       <c r="F27" s="36" t="s">
-        <v>319</v>
+        <v>365</v>
       </c>
       <c r="G27" s="36"/>
       <c r="H27" s="36"/>
       <c r="I27" s="36"/>
       <c r="J27" s="36" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K27" s="36"/>
       <c r="L27" s="36"/>
@@ -44169,24 +44169,24 @@
         <v>3</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D40" s="38"/>
       <c r="E40" s="38"/>
       <c r="F40" s="36" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G40" s="36"/>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
       <c r="J40" s="36" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K40" s="36"/>
       <c r="L40" s="36"/>
       <c r="M40" s="36"/>
       <c r="N40" s="36" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O40" s="36"/>
       <c r="P40" s="36"/>
@@ -44552,19 +44552,19 @@
       <c r="D53" s="38"/>
       <c r="E53" s="38"/>
       <c r="F53" s="36" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G53" s="36"/>
       <c r="H53" s="36"/>
       <c r="I53" s="36"/>
       <c r="J53" s="36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K53" s="36"/>
       <c r="L53" s="36"/>
       <c r="M53" s="36"/>
       <c r="N53" s="36" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="O53" s="36"/>
       <c r="P53" s="36"/>

--- a/resource/deta_godo.xlsx
+++ b/resource/deta_godo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cre\Desktop\ddd\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572AB9B7-50D2-4E29-AE2F-8D573DAA2D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BFB4E5-BDB0-4530-BE2E-4B6BA367E35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-45" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-336" yWindow="876" windowWidth="21600" windowHeight="11232" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ステージ" sheetId="1" r:id="rId1"/>
@@ -4034,34 +4034,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>消化効率+5%（この効果は最大20%まで。同種同名の花同士で有効な効果量上限は共有される。メイン効果とサブ効果は同じ上限を共有する。）</t>
-    <rPh sb="0" eb="2">
-      <t>ショウカ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウリツ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>サイダイ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ドウシ</t>
-    </rPh>
-    <rPh sb="33" eb="36">
-      <t>コウカリョウ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ジョウゲン</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>キョウユウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>プレイヤーのHPがゼロになった時、回復するHPがHP上限+50%分、増加する。この効果が発動するごとに残基-1。</t>
     <rPh sb="15" eb="16">
       <t>トキ</t>
@@ -4147,20 +4119,6 @@
     </rPh>
     <rPh sb="46" eb="48">
       <t>ショウメツ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>即時発動
-消化効率+15%（この種類の花で有効な効果量は最大20%まで。メイン効果とサブ効果は同じ上限を共有する。）</t>
-    <rPh sb="0" eb="4">
-      <t>ソクジハツドウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ショウカ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>コウリツ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -4183,6 +4141,48 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>即時発動
+消化間隔-15%（この種類の花で有効な効果量は最大20%まで。メイン効果とサブ効果は同じ上限を共有する。）</t>
+    <rPh sb="0" eb="4">
+      <t>ソクジハツドウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ショウカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンカク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>消化間隔-5%（この効果は最大20%まで。同種同名の花同士で有効な効果量上限は共有される。メイン効果とサブ効+C40:I52果は同じ上限を共有する。）</t>
+    <rPh sb="0" eb="2">
+      <t>ショウカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ドウシ</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>コウカリョウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ジョウゲン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>キョウユウ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -43413,7 +43413,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D14" s="38"/>
       <c r="E14" s="38"/>
@@ -43791,12 +43791,12 @@
         <v>2</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D27" s="38"/>
       <c r="E27" s="38"/>
       <c r="F27" s="36" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G27" s="36"/>
       <c r="H27" s="36"/>
@@ -44169,18 +44169,18 @@
         <v>3</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D40" s="38"/>
       <c r="E40" s="38"/>
       <c r="F40" s="36" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="G40" s="36"/>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
       <c r="J40" s="36" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K40" s="36"/>
       <c r="L40" s="36"/>
@@ -44552,19 +44552,19 @@
       <c r="D53" s="38"/>
       <c r="E53" s="38"/>
       <c r="F53" s="36" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G53" s="36"/>
       <c r="H53" s="36"/>
       <c r="I53" s="36"/>
       <c r="J53" s="36" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K53" s="36"/>
       <c r="L53" s="36"/>
       <c r="M53" s="36"/>
       <c r="N53" s="36" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O53" s="36"/>
       <c r="P53" s="36"/>

--- a/resource/deta_godo.xlsx
+++ b/resource/deta_godo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cre\Desktop\ddd\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4EB1325-1787-494B-B4F3-1D961C2D5271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F40CFDD-ACA9-408F-87B1-B96EE0ED9975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30810" yWindow="1080" windowWidth="21600" windowHeight="11295" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-144" yWindow="0" windowWidth="13944" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ステージ" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="377">
   <si>
     <t>NO</t>
   </si>
@@ -2728,25 +2728,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>HP1マス1の花びらが生成される。消化しても何も起こらない</t>
-    <rPh sb="7" eb="8">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ショウカ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ナニ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>何をさせたいスキル？：
 一番気持ちいい使い方：
 残基：
@@ -2828,20 +2809,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>悪夢から受けるダメージが30%上昇。
-ダメージを受けた時、次ターンの消化ダメージを受けたダメージの30%分上昇させる。</t>
-    <rPh sb="0" eb="2">
-      <t>アクム</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>1時までにステージをクリアすると永久に攻撃力が5%上昇する。（重複不可）</t>
     <rPh sb="1" eb="2">
       <t>ジ</t>
@@ -2982,67 +2949,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>HP現在の消化ダメージ500%、く型マスの花びらを生成する。
-消化されたとき、消化されるまでに受けた消化ダメージを隣接するモノに分配して与える。</t>
-    <rPh sb="2" eb="4">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ショウカ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ガタ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ショウカ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ショウカ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>ショウカ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>ブンパイ</t>
-    </rPh>
-    <rPh sb="68" eb="69">
-      <t>アタ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>HP1,マス1
-消化されたとき、隣接する花の受ける消化ダメージとHPを100%上昇する</t>
-    <rPh sb="8" eb="10">
-      <t>ショウカ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>リンセツ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ショウカ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>消化ダメージ+10%</t>
     <rPh sb="0" eb="2">
       <t>ショウカ</t>
@@ -3138,81 +3044,6 @@
     </rPh>
     <rPh sb="42" eb="44">
       <t>ザンキ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>即時発動
-HP5%回復</t>
-    <rPh sb="0" eb="4">
-      <t>ソクジハツドウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カイフク</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>即時発動型。
-消化が進むときの時間経過を通常の50%遅くする。この効果は4回発動すると消える。</t>
-    <rPh sb="0" eb="2">
-      <t>ソクジ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ハツドウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ガタ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ショウカ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>スス</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ケイカ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>オソ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="37" eb="40">
-      <t>カイハツドウ</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>消化ダメージ量+10%
-消化中の消化ダメージアップ効果が200%上昇する。</t>
-    <rPh sb="0" eb="2">
-      <t>ショウカ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>リョウ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>ショウカチュウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ショウカ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ジョウショウ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -3981,34 +3812,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>プレイヤーのHPがゼロになった時、回復するHPがHP上限+50%分、増加する。この効果が発動するごとに残基-1。</t>
-    <rPh sb="15" eb="16">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カイフク</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ジョウゲン</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ゾウカ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ハツドウ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>ザンキ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>何をさせたいスキル？：復活時のデメリットを減らしたい
 一番気持ちいい使い方：復活時の回復量を増やしてゾンビ
 残基：３
@@ -4031,41 +3834,6 @@
     </rPh>
     <rPh sb="54" eb="56">
       <t>ザンキ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>即時発動
-HPがゼロになっても追加の時間経過が発生しない。この効果が1回発動するとこの効果は消滅する。</t>
-    <rPh sb="0" eb="4">
-      <t>ソクジハツドウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ケイカ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ハツドウ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>ショウメツ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -4092,65 +3860,198 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>即時発動
-消化間隔-15%（この種類の花で有効な効果量は最大20%まで。メイン効果とサブ効果は同じ上限を共有する。）</t>
-    <rPh sb="0" eb="4">
-      <t>ソクジハツドウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ショウカ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カンカク</t>
-    </rPh>
+    <t>即時発動。HP5%回復</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>消化間隔-5%（この効果は最大20%まで。同種同名の花同士で有効な効果量上限は共有される。メイン効果とサブ効果は同じ上限を共有する。）</t>
+    <t>消化間隔-5%。この花はひとつしか持てない</t>
     <rPh sb="0" eb="2">
       <t>ショウカ</t>
     </rPh>
     <rPh sb="2" eb="4">
       <t>カンカク</t>
     </rPh>
-    <rPh sb="10" eb="12">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>サイダイ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ドウシ</t>
-    </rPh>
-    <rPh sb="33" eb="36">
-      <t>コウカリョウ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ジョウゲン</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>キョウユウ</t>
-    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>即時発動。消化間隔-15%</t>
+    <rPh sb="0" eb="2">
+      <t>ソクジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ショウカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンカク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>蘇生時の回復量がHP上限+50%増加。この効果が発動するごとに残基-1。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>即時発動。蘇生時の時間経過が発生しない。回数：1回</t>
+    <rPh sb="0" eb="2">
+      <t>ソクジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソセイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケイカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>HP1マス1の花びらが生成される。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>受けるダメージ+30%。受けたダメージ30%分を次の消化ダメージに加算。</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ショウカ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カサン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>HP現在の消化ダメージ500%、く型マスの花びらを生成する。消化時、受けた総合消化ダメージ100%を隣接するモノに分配して与える。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>即時発動型。時間経過を通常の50%遅くする。4回発動可能</t>
+    <rPh sb="0" eb="2">
+      <t>ソクジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ケイカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オソ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>クリア時にHPを回復出来なくなる。4時以降にクリア時夢の種を追加で1回獲得できる。</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>時刻が4時以降のとき消化ダメージが200%上昇する。</t>
-    <rPh sb="0" eb="2">
-      <t>ジコク</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ジイコウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ショウカ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ジョウショウ</t>
-    </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>ステージクリアでHPを回復出来なくなる。4時以降にステージをクリアすると夢の種を追加で1回獲得できる。</t>
+    <t>消化ダメージ量+10%。消化中の消化ダメージアップ効果が200%上昇する。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>HP1,マス1。消化時隣接する花のHPと受ける消化ダメージを100%上昇する</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ザイカ行政区</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ルノヴァ旧市街</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>フェリス庭区</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>エラミア区</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>大樹リラン駐屯地</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ミルネ街</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>コロッタ街</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ネリクス魔法学校</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>エルメナ大学</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ゴンサル地区</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>イリユ洞窟</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -4685,7 +4586,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I819"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
@@ -17214,7 +17115,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C959AC5-8D67-4CF8-8D3F-6E3C60C27AAC}">
   <dimension ref="A2:Z44"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="1:26">
       <c r="A2" s="8" t="s">
@@ -17236,10 +17137,10 @@
         <v>267</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="X2" s="8" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -17263,13 +17164,13 @@
         <v>268</v>
       </c>
       <c r="U3" s="8" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" ht="17.649999999999999" customHeight="1">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="17.7" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>249</v>
       </c>
@@ -17291,11 +17192,11 @@
       </c>
       <c r="R4" s="7"/>
       <c r="U4" s="36" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="V4" s="37"/>
       <c r="Y4" s="36" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="Z4" s="36"/>
     </row>
@@ -17385,7 +17286,7 @@
       <c r="U9" s="44"/>
       <c r="V9" s="44"/>
       <c r="Y9" s="8" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:26">
@@ -17396,7 +17297,7 @@
       <c r="U10" s="44"/>
       <c r="V10" s="44"/>
       <c r="Y10" s="36" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="Z10" s="37"/>
     </row>
@@ -17407,7 +17308,7 @@
       <c r="Y11" s="37"/>
       <c r="Z11" s="37"/>
     </row>
-    <row r="12" spans="1:26" ht="17.649999999999999" customHeight="1">
+    <row r="12" spans="1:26" ht="17.7" customHeight="1">
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
       <c r="U12" s="44"/>
@@ -17436,7 +17337,7 @@
     </row>
     <row r="16" spans="1:26">
       <c r="Y16" s="36" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="Z16" s="37"/>
     </row>
@@ -17454,12 +17355,12 @@
     </row>
     <row r="20" spans="25:26">
       <c r="Y20" s="8" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21" spans="25:26">
       <c r="Y21" s="36" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="Z21" s="37"/>
     </row>
@@ -17477,12 +17378,12 @@
     </row>
     <row r="25" spans="25:26">
       <c r="Y25" s="8" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="26" spans="25:26" ht="17.649999999999999" customHeight="1">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="26" spans="25:26" ht="17.7" customHeight="1">
       <c r="Y26" s="36" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="Z26" s="36"/>
     </row>
@@ -17504,12 +17405,12 @@
     </row>
     <row r="31" spans="25:26">
       <c r="Y31" s="8" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="32" spans="25:26" ht="17.649999999999999" customHeight="1">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="32" spans="25:26" ht="17.7" customHeight="1">
       <c r="Y32" s="36" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="Z32" s="36"/>
     </row>
@@ -17544,7 +17445,7 @@
     </row>
     <row r="40" spans="25:26">
       <c r="Y40" s="36" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="Z40" s="37"/>
     </row>
@@ -17591,7 +17492,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:D17"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
@@ -17608,8 +17509,8 @@
       <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
+      <c r="B3" s="8" t="s">
+        <v>367</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -17619,8 +17520,8 @@
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
+      <c r="B4" s="8" t="s">
+        <v>369</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -17630,8 +17531,8 @@
       <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
+      <c r="B5" s="8" t="s">
+        <v>374</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -17641,8 +17542,8 @@
       <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
-        <v>19</v>
+      <c r="B6" s="8" t="s">
+        <v>375</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -17653,7 +17554,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>370</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
@@ -17663,8 +17564,8 @@
       <c r="A8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
-        <v>25</v>
+      <c r="B8" s="8" t="s">
+        <v>368</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
@@ -17674,8 +17575,8 @@
       <c r="A9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" t="s">
-        <v>28</v>
+      <c r="B9" s="8" t="s">
+        <v>373</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -17685,8 +17586,8 @@
       <c r="A10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
-        <v>31</v>
+      <c r="B10" s="8" t="s">
+        <v>366</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -17696,8 +17597,8 @@
       <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
-        <v>34</v>
+      <c r="B11" s="8" t="s">
+        <v>371</v>
       </c>
       <c r="D11" t="s">
         <v>35</v>
@@ -17707,8 +17608,8 @@
       <c r="A12" t="s">
         <v>36</v>
       </c>
-      <c r="B12" t="s">
-        <v>37</v>
+      <c r="B12" s="8" t="s">
+        <v>372</v>
       </c>
       <c r="D12" t="s">
         <v>38</v>
@@ -17718,8 +17619,8 @@
       <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="s">
-        <v>40</v>
+      <c r="B13" s="8" t="s">
+        <v>376</v>
       </c>
       <c r="D13" t="s">
         <v>41</v>
@@ -17739,7 +17640,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:D4"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
@@ -17774,7 +17675,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:D3"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
@@ -17801,9 +17702,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="35.375" customWidth="1"/>
+    <col min="1" max="1" width="35.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18271,12 +18172,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA5628B-57DF-418D-BF0F-E86C8FCA0DD9}">
   <dimension ref="B2:F30"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="19.875" customWidth="1"/>
-    <col min="3" max="3" width="90.75" customWidth="1"/>
-    <col min="4" max="4" width="40.125" customWidth="1"/>
-    <col min="5" max="5" width="43.75" customWidth="1"/>
+    <col min="2" max="2" width="19.8984375" customWidth="1"/>
+    <col min="3" max="3" width="90.69921875" customWidth="1"/>
+    <col min="4" max="4" width="40.09765625" customWidth="1"/>
+    <col min="5" max="5" width="43.69921875" customWidth="1"/>
     <col min="6" max="6" width="67.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18782,7 +18683,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FDAC726-4736-4806-81DB-E0C12BC01725}">
   <dimension ref="A1:Z370"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:26">
       <c r="A1" s="41" t="s">
@@ -19091,7 +18992,7 @@
       <c r="D11" s="34"/>
       <c r="E11" s="34"/>
       <c r="F11" s="36" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="G11" s="37"/>
       <c r="H11" s="37"/>
@@ -19103,7 +19004,7 @@
       <c r="L11" s="34"/>
       <c r="M11" s="34"/>
       <c r="N11" s="39" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="O11" s="40"/>
       <c r="P11" s="40"/>
@@ -19383,7 +19284,7 @@
       <c r="D21" s="34"/>
       <c r="E21" s="34"/>
       <c r="F21" s="36" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G21" s="37"/>
       <c r="H21" s="37"/>
@@ -19406,7 +19307,7 @@
       <c r="U21" s="40"/>
       <c r="V21" s="40"/>
       <c r="W21" s="36" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="X21" s="37"/>
       <c r="Y21" s="37"/>
@@ -19675,7 +19576,7 @@
       <c r="D31" s="34"/>
       <c r="E31" s="34"/>
       <c r="F31" s="36" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="G31" s="37"/>
       <c r="H31" s="37"/>
@@ -19967,7 +19868,7 @@
       <c r="D41" s="34"/>
       <c r="E41" s="34"/>
       <c r="F41" s="36" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="G41" s="37"/>
       <c r="H41" s="37"/>
@@ -19990,7 +19891,7 @@
       <c r="U41" s="40"/>
       <c r="V41" s="40"/>
       <c r="W41" s="36" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="X41" s="37"/>
       <c r="Y41" s="37"/>
@@ -20261,7 +20162,7 @@
       <c r="D51" s="34"/>
       <c r="E51" s="34"/>
       <c r="F51" s="36" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="G51" s="37"/>
       <c r="H51" s="37"/>
@@ -20553,7 +20454,7 @@
       <c r="D61" s="34"/>
       <c r="E61" s="34"/>
       <c r="F61" s="36" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="G61" s="37"/>
       <c r="H61" s="37"/>
@@ -20845,7 +20746,7 @@
       <c r="D71" s="34"/>
       <c r="E71" s="34"/>
       <c r="F71" s="36" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="G71" s="37"/>
       <c r="H71" s="37"/>
@@ -20857,7 +20758,7 @@
       <c r="L71" s="34"/>
       <c r="M71" s="34"/>
       <c r="N71" s="39" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="O71" s="40"/>
       <c r="P71" s="40"/>
@@ -21137,7 +21038,7 @@
       <c r="D81" s="34"/>
       <c r="E81" s="34"/>
       <c r="F81" s="36" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="G81" s="37"/>
       <c r="H81" s="37"/>
@@ -21431,7 +21332,7 @@
       <c r="D91" s="34"/>
       <c r="E91" s="34"/>
       <c r="F91" s="36" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="G91" s="37"/>
       <c r="H91" s="37"/>
@@ -21443,7 +21344,7 @@
       <c r="L91" s="34"/>
       <c r="M91" s="34"/>
       <c r="N91" s="39" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="O91" s="40"/>
       <c r="P91" s="40"/>
@@ -21723,7 +21624,7 @@
       <c r="D101" s="34"/>
       <c r="E101" s="34"/>
       <c r="F101" s="36" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="G101" s="37"/>
       <c r="H101" s="37"/>
@@ -22015,7 +21916,7 @@
       <c r="D111" s="34"/>
       <c r="E111" s="34"/>
       <c r="F111" s="36" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="G111" s="37"/>
       <c r="H111" s="37"/>
@@ -22307,7 +22208,7 @@
       <c r="D121" s="34"/>
       <c r="E121" s="34"/>
       <c r="F121" s="36" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="G121" s="37"/>
       <c r="H121" s="37"/>
@@ -29851,7 +29752,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6D2EFC-47F0-4DB9-83BC-DD958DB4244A}">
   <dimension ref="A1:Z445"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:26">
       <c r="A1" s="38" t="s">
@@ -29911,7 +29812,7 @@
       <c r="L4" s="36"/>
       <c r="M4" s="36"/>
       <c r="N4" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O4" s="36"/>
       <c r="P4" s="36"/>
@@ -30283,13 +30184,13 @@
       <c r="H17" s="36"/>
       <c r="I17" s="36"/>
       <c r="J17" s="36" t="s">
-        <v>302</v>
+        <v>358</v>
       </c>
       <c r="K17" s="36"/>
       <c r="L17" s="36"/>
       <c r="M17" s="36"/>
       <c r="N17" s="36" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O17" s="36"/>
       <c r="P17" s="36"/>
@@ -30655,19 +30556,19 @@
       <c r="D30" s="38"/>
       <c r="E30" s="38"/>
       <c r="F30" s="36" t="s">
-        <v>306</v>
+        <v>359</v>
       </c>
       <c r="G30" s="36"/>
       <c r="H30" s="36"/>
       <c r="I30" s="36"/>
       <c r="J30" s="36" t="s">
-        <v>312</v>
+        <v>360</v>
       </c>
       <c r="K30" s="36"/>
       <c r="L30" s="36"/>
       <c r="M30" s="36"/>
       <c r="N30" s="36" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O30" s="36"/>
       <c r="P30" s="36"/>
@@ -31033,19 +30934,19 @@
       <c r="D43" s="38"/>
       <c r="E43" s="38"/>
       <c r="F43" s="36" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G43" s="36"/>
       <c r="H43" s="36"/>
       <c r="I43" s="36"/>
       <c r="J43" s="36" t="s">
-        <v>320</v>
+        <v>361</v>
       </c>
       <c r="K43" s="36"/>
       <c r="L43" s="36"/>
       <c r="M43" s="36"/>
       <c r="N43" s="36" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="O43" s="36"/>
       <c r="P43" s="36"/>
@@ -31400,7 +31301,7 @@
     </row>
     <row r="56" spans="1:26" ht="18.75" customHeight="1">
       <c r="A56" s="41" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B56" s="34">
         <v>4</v>
@@ -31411,19 +31312,19 @@
       <c r="D56" s="38"/>
       <c r="E56" s="38"/>
       <c r="F56" s="36" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G56" s="36"/>
       <c r="H56" s="36"/>
       <c r="I56" s="36"/>
       <c r="J56" s="36" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K56" s="36"/>
       <c r="L56" s="36"/>
       <c r="M56" s="36"/>
       <c r="N56" s="36" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="O56" s="36"/>
       <c r="P56" s="36"/>
@@ -31789,19 +31690,19 @@
       <c r="D69" s="38"/>
       <c r="E69" s="38"/>
       <c r="F69" s="36" t="s">
-        <v>321</v>
+        <v>364</v>
       </c>
       <c r="G69" s="36"/>
       <c r="H69" s="36"/>
       <c r="I69" s="36"/>
       <c r="J69" s="36" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="K69" s="36"/>
       <c r="L69" s="36"/>
       <c r="M69" s="36"/>
       <c r="N69" s="36" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="O69" s="36"/>
       <c r="P69" s="36"/>
@@ -32179,7 +32080,7 @@
       <c r="L82" s="36"/>
       <c r="M82" s="36"/>
       <c r="N82" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O82" s="36"/>
       <c r="P82" s="36"/>
@@ -32557,7 +32458,7 @@
       <c r="L95" s="36"/>
       <c r="M95" s="36"/>
       <c r="N95" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O95" s="36"/>
       <c r="P95" s="36"/>
@@ -32935,7 +32836,7 @@
       <c r="L108" s="36"/>
       <c r="M108" s="36"/>
       <c r="N108" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O108" s="36"/>
       <c r="P108" s="36"/>
@@ -33313,7 +33214,7 @@
       <c r="L121" s="36"/>
       <c r="M121" s="36"/>
       <c r="N121" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O121" s="36"/>
       <c r="P121" s="36"/>
@@ -33691,7 +33592,7 @@
       <c r="L134" s="36"/>
       <c r="M134" s="36"/>
       <c r="N134" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O134" s="36"/>
       <c r="P134" s="36"/>
@@ -34069,7 +33970,7 @@
       <c r="L147" s="36"/>
       <c r="M147" s="36"/>
       <c r="N147" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O147" s="36"/>
       <c r="P147" s="36"/>
@@ -34447,7 +34348,7 @@
       <c r="L160" s="36"/>
       <c r="M160" s="36"/>
       <c r="N160" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O160" s="36"/>
       <c r="P160" s="36"/>
@@ -34825,7 +34726,7 @@
       <c r="L173" s="36"/>
       <c r="M173" s="36"/>
       <c r="N173" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O173" s="36"/>
       <c r="P173" s="36"/>
@@ -35203,7 +35104,7 @@
       <c r="L186" s="36"/>
       <c r="M186" s="36"/>
       <c r="N186" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O186" s="36"/>
       <c r="P186" s="36"/>
@@ -35581,7 +35482,7 @@
       <c r="L199" s="36"/>
       <c r="M199" s="36"/>
       <c r="N199" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O199" s="36"/>
       <c r="P199" s="36"/>
@@ -35959,7 +35860,7 @@
       <c r="L212" s="36"/>
       <c r="M212" s="36"/>
       <c r="N212" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O212" s="36"/>
       <c r="P212" s="36"/>
@@ -36337,7 +36238,7 @@
       <c r="L225" s="36"/>
       <c r="M225" s="36"/>
       <c r="N225" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O225" s="36"/>
       <c r="P225" s="36"/>
@@ -36715,7 +36616,7 @@
       <c r="L238" s="36"/>
       <c r="M238" s="36"/>
       <c r="N238" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O238" s="36"/>
       <c r="P238" s="36"/>
@@ -37093,7 +36994,7 @@
       <c r="L251" s="36"/>
       <c r="M251" s="36"/>
       <c r="N251" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O251" s="36"/>
       <c r="P251" s="36"/>
@@ -37471,7 +37372,7 @@
       <c r="L264" s="36"/>
       <c r="M264" s="36"/>
       <c r="N264" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O264" s="36"/>
       <c r="P264" s="36"/>
@@ -37849,7 +37750,7 @@
       <c r="L277" s="36"/>
       <c r="M277" s="36"/>
       <c r="N277" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O277" s="36"/>
       <c r="P277" s="36"/>
@@ -38227,7 +38128,7 @@
       <c r="L290" s="36"/>
       <c r="M290" s="36"/>
       <c r="N290" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O290" s="36"/>
       <c r="P290" s="36"/>
@@ -38605,7 +38506,7 @@
       <c r="L303" s="36"/>
       <c r="M303" s="36"/>
       <c r="N303" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O303" s="36"/>
       <c r="P303" s="36"/>
@@ -38983,7 +38884,7 @@
       <c r="L316" s="36"/>
       <c r="M316" s="36"/>
       <c r="N316" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O316" s="36"/>
       <c r="P316" s="36"/>
@@ -39361,7 +39262,7 @@
       <c r="L329" s="36"/>
       <c r="M329" s="36"/>
       <c r="N329" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O329" s="36"/>
       <c r="P329" s="36"/>
@@ -39739,7 +39640,7 @@
       <c r="L342" s="36"/>
       <c r="M342" s="36"/>
       <c r="N342" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O342" s="36"/>
       <c r="P342" s="36"/>
@@ -40117,7 +40018,7 @@
       <c r="L355" s="36"/>
       <c r="M355" s="36"/>
       <c r="N355" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O355" s="36"/>
       <c r="P355" s="36"/>
@@ -40495,7 +40396,7 @@
       <c r="L368" s="36"/>
       <c r="M368" s="36"/>
       <c r="N368" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O368" s="36"/>
       <c r="P368" s="36"/>
@@ -40873,7 +40774,7 @@
       <c r="L381" s="36"/>
       <c r="M381" s="36"/>
       <c r="N381" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O381" s="36"/>
       <c r="P381" s="36"/>
@@ -41251,7 +41152,7 @@
       <c r="L394" s="36"/>
       <c r="M394" s="36"/>
       <c r="N394" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O394" s="36"/>
       <c r="P394" s="36"/>
@@ -41629,7 +41530,7 @@
       <c r="L407" s="36"/>
       <c r="M407" s="36"/>
       <c r="N407" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O407" s="36"/>
       <c r="P407" s="36"/>
@@ -42007,7 +41908,7 @@
       <c r="L420" s="36"/>
       <c r="M420" s="36"/>
       <c r="N420" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O420" s="36"/>
       <c r="P420" s="36"/>
@@ -42385,7 +42286,7 @@
       <c r="L433" s="36"/>
       <c r="M433" s="36"/>
       <c r="N433" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O433" s="36"/>
       <c r="P433" s="36"/>
@@ -42992,7 +42893,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCCBED2E-6CBB-4FE7-BB78-40B976DF6037}">
   <dimension ref="A1:Z260"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:26">
       <c r="A1" s="41" t="s">
@@ -43019,7 +42920,7 @@
       <c r="L1" s="36"/>
       <c r="M1" s="36"/>
       <c r="N1" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O1" s="36"/>
       <c r="P1" s="36"/>
@@ -43377,27 +43278,27 @@
         <v>285</v>
       </c>
       <c r="B14" s="34">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="D14" s="38"/>
       <c r="E14" s="38"/>
       <c r="F14" s="36" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G14" s="36"/>
       <c r="H14" s="36"/>
       <c r="I14" s="36"/>
       <c r="J14" s="36" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="K14" s="36"/>
       <c r="L14" s="36"/>
       <c r="M14" s="36"/>
       <c r="N14" s="36" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="O14" s="36"/>
       <c r="P14" s="36"/>
@@ -43755,27 +43656,27 @@
         <v>285</v>
       </c>
       <c r="B27" s="34">
-        <v>2</v>
+        <v>1002</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="D27" s="38"/>
       <c r="E27" s="38"/>
       <c r="F27" s="36" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="G27" s="36"/>
       <c r="H27" s="36"/>
       <c r="I27" s="36"/>
       <c r="J27" s="36" t="s">
-        <v>319</v>
+        <v>353</v>
       </c>
       <c r="K27" s="36"/>
       <c r="L27" s="36"/>
       <c r="M27" s="36"/>
       <c r="N27" s="36" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="O27" s="36"/>
       <c r="P27" s="36"/>
@@ -44133,27 +44034,27 @@
         <v>285</v>
       </c>
       <c r="B40" s="34">
-        <v>3</v>
+        <v>1003</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="D40" s="38"/>
       <c r="E40" s="38"/>
       <c r="F40" s="36" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="G40" s="36"/>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
       <c r="J40" s="36" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="K40" s="36"/>
       <c r="L40" s="36"/>
       <c r="M40" s="36"/>
       <c r="N40" s="36" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="O40" s="36"/>
       <c r="P40" s="36"/>
@@ -44511,7 +44412,7 @@
         <v>285</v>
       </c>
       <c r="B53" s="34">
-        <v>4</v>
+        <v>1004</v>
       </c>
       <c r="C53" s="38" t="s">
         <v>286</v>
@@ -44519,7 +44420,7 @@
       <c r="D53" s="38"/>
       <c r="E53" s="38"/>
       <c r="F53" s="36" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G53" s="36"/>
       <c r="H53" s="36"/>
@@ -44531,7 +44432,7 @@
       <c r="L53" s="36"/>
       <c r="M53" s="36"/>
       <c r="N53" s="36" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="O53" s="36"/>
       <c r="P53" s="36"/>
@@ -44889,7 +44790,7 @@
         <v>285</v>
       </c>
       <c r="B66" s="34">
-        <v>5</v>
+        <v>1005</v>
       </c>
       <c r="C66" s="38" t="s">
         <v>286</v>
@@ -44909,7 +44810,7 @@
       <c r="L66" s="36"/>
       <c r="M66" s="36"/>
       <c r="N66" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O66" s="36"/>
       <c r="P66" s="36"/>
@@ -45267,7 +45168,7 @@
         <v>285</v>
       </c>
       <c r="B79" s="34">
-        <v>6</v>
+        <v>1006</v>
       </c>
       <c r="C79" s="38" t="s">
         <v>286</v>
@@ -45287,7 +45188,7 @@
       <c r="L79" s="36"/>
       <c r="M79" s="36"/>
       <c r="N79" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O79" s="36"/>
       <c r="P79" s="36"/>
@@ -45645,7 +45546,7 @@
         <v>285</v>
       </c>
       <c r="B92" s="34">
-        <v>7</v>
+        <v>1007</v>
       </c>
       <c r="C92" s="38" t="s">
         <v>286</v>
@@ -45665,7 +45566,7 @@
       <c r="L92" s="36"/>
       <c r="M92" s="36"/>
       <c r="N92" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O92" s="36"/>
       <c r="P92" s="36"/>
@@ -46023,7 +45924,7 @@
         <v>285</v>
       </c>
       <c r="B105" s="34">
-        <v>8</v>
+        <v>1008</v>
       </c>
       <c r="C105" s="38" t="s">
         <v>286</v>
@@ -46043,7 +45944,7 @@
       <c r="L105" s="36"/>
       <c r="M105" s="36"/>
       <c r="N105" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O105" s="36"/>
       <c r="P105" s="36"/>
@@ -46401,7 +46302,7 @@
         <v>285</v>
       </c>
       <c r="B118" s="34">
-        <v>9</v>
+        <v>1009</v>
       </c>
       <c r="C118" s="38" t="s">
         <v>286</v>
@@ -46421,7 +46322,7 @@
       <c r="L118" s="36"/>
       <c r="M118" s="36"/>
       <c r="N118" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O118" s="36"/>
       <c r="P118" s="36"/>
@@ -46779,7 +46680,7 @@
         <v>285</v>
       </c>
       <c r="B131" s="34">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="C131" s="38" t="s">
         <v>286</v>
@@ -46799,7 +46700,7 @@
       <c r="L131" s="36"/>
       <c r="M131" s="36"/>
       <c r="N131" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O131" s="36"/>
       <c r="P131" s="36"/>
@@ -47157,7 +47058,7 @@
         <v>285</v>
       </c>
       <c r="B144" s="34">
-        <v>11</v>
+        <v>1011</v>
       </c>
       <c r="C144" s="38" t="s">
         <v>286</v>
@@ -47177,7 +47078,7 @@
       <c r="L144" s="36"/>
       <c r="M144" s="36"/>
       <c r="N144" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O144" s="36"/>
       <c r="P144" s="36"/>
@@ -47535,7 +47436,7 @@
         <v>285</v>
       </c>
       <c r="B157" s="34">
-        <v>12</v>
+        <v>1012</v>
       </c>
       <c r="C157" s="38" t="s">
         <v>286</v>
@@ -47555,7 +47456,7 @@
       <c r="L157" s="36"/>
       <c r="M157" s="36"/>
       <c r="N157" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O157" s="36"/>
       <c r="P157" s="36"/>
@@ -47913,7 +47814,7 @@
         <v>285</v>
       </c>
       <c r="B170" s="34">
-        <v>13</v>
+        <v>1013</v>
       </c>
       <c r="C170" s="38" t="s">
         <v>286</v>
@@ -47933,7 +47834,7 @@
       <c r="L170" s="36"/>
       <c r="M170" s="36"/>
       <c r="N170" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O170" s="36"/>
       <c r="P170" s="36"/>
@@ -48291,7 +48192,7 @@
         <v>285</v>
       </c>
       <c r="B183" s="34">
-        <v>14</v>
+        <v>1014</v>
       </c>
       <c r="C183" s="38" t="s">
         <v>286</v>
@@ -48311,7 +48212,7 @@
       <c r="L183" s="36"/>
       <c r="M183" s="36"/>
       <c r="N183" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O183" s="36"/>
       <c r="P183" s="36"/>
@@ -48669,7 +48570,7 @@
         <v>285</v>
       </c>
       <c r="B196" s="34">
-        <v>15</v>
+        <v>1015</v>
       </c>
       <c r="C196" s="38" t="s">
         <v>286</v>
@@ -48689,7 +48590,7 @@
       <c r="L196" s="36"/>
       <c r="M196" s="36"/>
       <c r="N196" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O196" s="36"/>
       <c r="P196" s="36"/>
@@ -49047,7 +48948,7 @@
         <v>285</v>
       </c>
       <c r="B209" s="34">
-        <v>16</v>
+        <v>1016</v>
       </c>
       <c r="C209" s="38" t="s">
         <v>286</v>
@@ -49067,7 +48968,7 @@
       <c r="L209" s="36"/>
       <c r="M209" s="36"/>
       <c r="N209" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O209" s="36"/>
       <c r="P209" s="36"/>
@@ -49425,7 +49326,7 @@
         <v>285</v>
       </c>
       <c r="B222" s="34">
-        <v>17</v>
+        <v>1017</v>
       </c>
       <c r="C222" s="38" t="s">
         <v>286</v>
@@ -49445,7 +49346,7 @@
       <c r="L222" s="36"/>
       <c r="M222" s="36"/>
       <c r="N222" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O222" s="36"/>
       <c r="P222" s="36"/>
@@ -49803,7 +49704,7 @@
         <v>285</v>
       </c>
       <c r="B235" s="34">
-        <v>18</v>
+        <v>1018</v>
       </c>
       <c r="C235" s="38" t="s">
         <v>286</v>
@@ -49823,7 +49724,7 @@
       <c r="L235" s="36"/>
       <c r="M235" s="36"/>
       <c r="N235" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O235" s="36"/>
       <c r="P235" s="36"/>
@@ -50181,7 +50082,7 @@
         <v>285</v>
       </c>
       <c r="B248" s="34">
-        <v>19</v>
+        <v>1019</v>
       </c>
       <c r="C248" s="38" t="s">
         <v>286</v>
@@ -50201,7 +50102,7 @@
       <c r="L248" s="36"/>
       <c r="M248" s="36"/>
       <c r="N248" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O248" s="36"/>
       <c r="P248" s="36"/>
